--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{511593F8-FC50-4FAE-91E8-C0500B9A02AC}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21533F78-3999-4E23-BAF0-BAACBC6A2EF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,24 @@
   <si>
     <t>20026-09-04</t>
   </si>
+  <si>
+    <t>felling good</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>feelig good</t>
+  </si>
+  <si>
+    <t>feeling god</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
 </sst>
 </file>
 
@@ -380,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -425,6 +443,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1762,7 +1781,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
+      <c r="A22" s="22">
         <v>46275</v>
       </c>
       <c r="B22" s="14">
@@ -1808,114 +1827,234 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>420</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B24" s="14">
+        <v>500</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>90</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>45</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B25" s="14">
+        <v>520</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>100</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B26" s="14">
+        <v>600</v>
+      </c>
+      <c r="C26" s="14">
+        <v>15</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>480</v>
+      </c>
+      <c r="G26" s="14">
+        <v>6</v>
+      </c>
+      <c r="H26" s="14">
+        <v>45</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>120</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>25</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>75</v>
+      </c>
+      <c r="F27" s="14">
+        <v>480</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21533F78-3999-4E23-BAF0-BAACBC6A2EF1}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76734751-48B9-4B03-83DD-CF5705B486CE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -439,11 +439,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -931,74 +931,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12610019</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1781,7 +1781,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="22">
+      <c r="A22" s="18">
         <v>46275</v>
       </c>
       <c r="B22" s="14">
@@ -2057,26 +2057,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B28" s="14">
+        <v>460</v>
+      </c>
+      <c r="C28" s="14">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>75</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>430</v>
+      </c>
+      <c r="G28" s="14">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
+        <v>45</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="277" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76734751-48B9-4B03-83DD-CF5705B486CE}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B490229-E603-4C68-8F0A-1303AFC41569}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2103,26 +2103,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B29" s="14">
+        <v>500</v>
+      </c>
+      <c r="C29" s="14">
+        <v>25</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>45</v>
+      </c>
+      <c r="F29" s="14">
+        <v>400</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B490229-E603-4C68-8F0A-1303AFC41569}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2F0817-E7CE-48D3-9DE3-0AB223900626}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2149,92 +2149,188 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>45</v>
+      </c>
+      <c r="F30" s="14">
+        <v>400</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>35</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B31" s="14">
+        <v>580</v>
+      </c>
+      <c r="C31" s="14">
+        <v>35</v>
+      </c>
+      <c r="D31" s="14">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14">
+        <v>45</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>35</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>875</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>565</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B32" s="14">
+        <v>520</v>
+      </c>
+      <c r="C32" s="14">
+        <v>25</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>60</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>40</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>675</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>250</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>35</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>465</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/CAP776.xlsx
+++ b/CAP776.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a0fc1058fb35a12/Desktop/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B2F0817-E7CE-48D3-9DE3-0AB223900626}"/>
+  <xr:revisionPtr revIDLastSave="437" documentId="8_{B52B83EB-C9BE-48DA-91FE-F4A273B4E431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC2D596B-E032-4E2A-B2DC-AD827A74061B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,12 +216,6 @@
     <t>very tired after classes</t>
   </si>
   <si>
-    <t>2026-008-26</t>
-  </si>
-  <si>
-    <t>26-08-28</t>
-  </si>
-  <si>
     <t>feeling good</t>
   </si>
   <si>
@@ -398,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -439,7 +433,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -931,74 +924,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="21">
         <v>12610019</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1137,8 +1130,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>59</v>
+      <c r="A8" s="13">
+        <v>46260</v>
       </c>
       <c r="B8" s="14">
         <v>500</v>
@@ -1229,8 +1222,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>60</v>
+      <c r="A10" s="13">
+        <v>46262</v>
       </c>
       <c r="B10" s="14">
         <v>480</v>
@@ -1291,21 +1284,21 @@
         <v>50</v>
       </c>
       <c r="F11" s="14">
-        <v>430</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
         <v>45</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1175</v>
+        <v>745</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>695</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>57</v>
@@ -1363,7 +1356,7 @@
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1383,21 +1376,21 @@
         <v>50</v>
       </c>
       <c r="F13" s="14">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="G13" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="14">
         <v>30</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1160</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>57</v>
@@ -1409,7 +1402,7 @@
         <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1452,10 +1445,10 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1498,10 +1491,10 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1547,12 +1540,12 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B17" s="14">
         <v>480</v>
@@ -1590,10 +1583,10 @@
         <v>50</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1636,10 +1629,10 @@
         <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1682,15 +1675,15 @@
         <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B20" s="14">
         <v>480</v>
@@ -1728,15 +1721,15 @@
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B21" s="14">
         <v>440</v>
@@ -1774,15 +1767,15 @@
         <v>50</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="18">
-        <v>46275</v>
+      <c r="A22" s="13">
+        <v>46274</v>
       </c>
       <c r="B22" s="14">
         <v>420</v>
@@ -1820,15 +1813,15 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B23" s="14">
         <v>420</v>
@@ -1866,15 +1859,15 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B24" s="14">
         <v>500</v>
@@ -1906,21 +1899,21 @@
         <v>595</v>
       </c>
       <c r="K24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N24" s="17" t="s">
         <v>67</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B25" s="14">
         <v>520</v>
@@ -1958,15 +1951,15 @@
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B26" s="14">
         <v>600</v>
@@ -2007,12 +2000,12 @@
         <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B27" s="14">
         <v>480</v>
@@ -2050,15 +2043,15 @@
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B28" s="14">
         <v>460</v>
@@ -2099,12 +2092,12 @@
         <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B29" s="14">
         <v>500</v>
@@ -2145,12 +2138,12 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B30" s="14">
         <v>480</v>
@@ -2191,12 +2184,12 @@
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B31" s="14">
         <v>580</v>
@@ -2237,12 +2230,12 @@
         <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B32" s="14">
         <v>520</v>
@@ -2283,12 +2276,12 @@
         <v>51</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B33" s="14">
         <v>480</v>
@@ -2329,96 +2322,192 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B34" s="14">
+        <v>500</v>
+      </c>
+      <c r="C34" s="14">
+        <v>35</v>
+      </c>
+      <c r="D34" s="14">
+        <v>90</v>
+      </c>
+      <c r="E34" s="14">
+        <v>45</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>35</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B35" s="14">
+        <v>480</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>80</v>
+      </c>
+      <c r="E35" s="14">
+        <v>50</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>6</v>
+      </c>
+      <c r="H35" s="14">
+        <v>36</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1026</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>414</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B36" s="14">
+        <v>460</v>
+      </c>
+      <c r="C36" s="14">
+        <v>25</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>45</v>
+      </c>
+      <c r="F36" s="14">
+        <v>400</v>
+      </c>
+      <c r="G36" s="14">
+        <v>7</v>
+      </c>
+      <c r="H36" s="14">
+        <v>40</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B37" s="14">
+        <v>490</v>
+      </c>
+      <c r="C37" s="14">
+        <v>25</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>50</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14">
+        <v>30</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
